--- a/travel_data_dictionary_10_countries.xlsx
+++ b/travel_data_dictionary_10_countries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/me/Documents/Analyticon 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DF1A37-320C-A340-A12C-CE0758DA4BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8115C6EE-6A7A-9740-9C22-6A92067D4BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3280" yWindow="660" windowWidth="24180" windowHeight="20080" firstSheet="3" activeTab="11" xr2:uid="{A2AB0F8D-C7A1-F845-BEBD-0B60C6287839}"/>
+    <workbookView xWindow="38680" yWindow="780" windowWidth="24180" windowHeight="19900" firstSheet="3" activeTab="11" xr2:uid="{A2AB0F8D-C7A1-F845-BEBD-0B60C6287839}"/>
   </bookViews>
   <sheets>
     <sheet name="country_master" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="327">
   <si>
     <t>country</t>
   </si>
@@ -1014,6 +1014,24 @@
   </si>
   <si>
     <t>'/Users/me/Documents/Analyticon 2026/images/us/us_night.jpeg'</t>
+  </si>
+  <si>
+    <t>Street Transport</t>
+  </si>
+  <si>
+    <t>Ancient Ruins</t>
+  </si>
+  <si>
+    <t>Mountain Cable Car</t>
+  </si>
+  <si>
+    <t>White Church</t>
+  </si>
+  <si>
+    <t>New York Taxi</t>
+  </si>
+  <si>
+    <t>Hollywood Sign</t>
   </si>
 </sst>
 </file>
@@ -2046,8 +2064,8 @@
       <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>192</v>
+      <c r="B9" t="s">
+        <v>321</v>
       </c>
       <c r="C9" t="s">
         <v>302</v>
@@ -2112,8 +2130,8 @@
       <c r="A15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>193</v>
+      <c r="B15" t="s">
+        <v>322</v>
       </c>
       <c r="C15" t="s">
         <v>295</v>
@@ -2156,8 +2174,8 @@
       <c r="A19" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>192</v>
+      <c r="B19" t="s">
+        <v>323</v>
       </c>
       <c r="C19" t="s">
         <v>313</v>
@@ -2167,8 +2185,8 @@
       <c r="A20" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>193</v>
+      <c r="B20" t="s">
+        <v>324</v>
       </c>
       <c r="C20" t="s">
         <v>314</v>
@@ -2211,8 +2229,8 @@
       <c r="A24" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>192</v>
+      <c r="B24" t="s">
+        <v>325</v>
       </c>
       <c r="C24" t="s">
         <v>318</v>
@@ -2222,8 +2240,8 @@
       <c r="A25" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>193</v>
+      <c r="B25" t="s">
+        <v>326</v>
       </c>
       <c r="C25" t="s">
         <v>319</v>
